--- a/models/Tarnoc_v2_aggressive_2026-09-07.xlsx
+++ b/models/Tarnoc_v2_aggressive_2026-09-07.xlsx
@@ -1203,7 +1203,7 @@
     <row r="38">
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Aggressive, EUR10m: 2,800 / 6,900 / 11,700 / 18,800 units, EUR321m revenue in 2030. Gross margin 28%, 38%, 37%, 37%. EBITDA +4.8m, +23m, +45m, +79m. 301 people.</t>
+          <t>Aggressive, EUR10m: 2,812 / 6,864 / 11,730 / 18,780 units, EUR321m revenue in 2030. Gross margin 28%, 38%, 37%, 37%. EBITDA +4.8m, +23m, +45m, +79m. 302 people.</t>
         </is>
       </c>
     </row>
@@ -22730,12 +22730,12 @@
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Reps hired</t>
+          <t>Rep hiring rate</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>FTE</t>
+          <t>FTE/month</t>
         </is>
       </c>
       <c r="E16" s="64">
@@ -23000,7 +23000,7 @@
       </c>
       <c r="BT16" s="32" t="inlineStr">
         <is>
-          <t>no sales reps before the first month we can sell</t>
+          <t>the planned rate, which can be less than one a month</t>
         </is>
       </c>
     </row>
@@ -23016,243 +23016,243 @@
         </is>
       </c>
       <c r="E17" s="13">
-        <f>Assumptions!$D$60+E16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:E16),0)</f>
         <v/>
       </c>
       <c r="F17" s="13">
-        <f>E17+F16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:F16),0)</f>
         <v/>
       </c>
       <c r="G17" s="13">
-        <f>F17+G16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:G16),0)</f>
         <v/>
       </c>
       <c r="H17" s="13">
-        <f>G17+H16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:H16),0)</f>
         <v/>
       </c>
       <c r="I17" s="13">
-        <f>H17+I16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:I16),0)</f>
         <v/>
       </c>
       <c r="J17" s="13">
-        <f>I17+J16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:J16),0)</f>
         <v/>
       </c>
       <c r="K17" s="13">
-        <f>J17+K16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:K16),0)</f>
         <v/>
       </c>
       <c r="L17" s="13">
-        <f>K17+L16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:L16),0)</f>
         <v/>
       </c>
       <c r="M17" s="13">
-        <f>L17+M16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:M16),0)</f>
         <v/>
       </c>
       <c r="N17" s="13">
-        <f>M17+N16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:N16),0)</f>
         <v/>
       </c>
       <c r="O17" s="13">
-        <f>N17+O16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:O16),0)</f>
         <v/>
       </c>
       <c r="P17" s="13">
-        <f>O17+P16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:P16),0)</f>
         <v/>
       </c>
       <c r="Q17" s="13">
-        <f>P17+Q16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:Q16),0)</f>
         <v/>
       </c>
       <c r="R17" s="13">
-        <f>Q17+R16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:R16),0)</f>
         <v/>
       </c>
       <c r="S17" s="13">
-        <f>R17+S16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:S16),0)</f>
         <v/>
       </c>
       <c r="T17" s="13">
-        <f>S17+T16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:T16),0)</f>
         <v/>
       </c>
       <c r="U17" s="13">
-        <f>T17+U16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:U16),0)</f>
         <v/>
       </c>
       <c r="V17" s="13">
-        <f>U17+V16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:V16),0)</f>
         <v/>
       </c>
       <c r="W17" s="13">
-        <f>V17+W16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:W16),0)</f>
         <v/>
       </c>
       <c r="X17" s="13">
-        <f>W17+X16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:X16),0)</f>
         <v/>
       </c>
       <c r="Y17" s="13">
-        <f>X17+Y16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:Y16),0)</f>
         <v/>
       </c>
       <c r="Z17" s="13">
-        <f>Y17+Z16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:Z16),0)</f>
         <v/>
       </c>
       <c r="AA17" s="13">
-        <f>Z17+AA16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AA16),0)</f>
         <v/>
       </c>
       <c r="AB17" s="13">
-        <f>AA17+AB16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AB16),0)</f>
         <v/>
       </c>
       <c r="AC17" s="13">
-        <f>AB17+AC16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AC16),0)</f>
         <v/>
       </c>
       <c r="AD17" s="13">
-        <f>AC17+AD16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AD16),0)</f>
         <v/>
       </c>
       <c r="AE17" s="13">
-        <f>AD17+AE16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AE16),0)</f>
         <v/>
       </c>
       <c r="AF17" s="13">
-        <f>AE17+AF16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AF16),0)</f>
         <v/>
       </c>
       <c r="AG17" s="13">
-        <f>AF17+AG16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AG16),0)</f>
         <v/>
       </c>
       <c r="AH17" s="13">
-        <f>AG17+AH16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AH16),0)</f>
         <v/>
       </c>
       <c r="AI17" s="13">
-        <f>AH17+AI16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AI16),0)</f>
         <v/>
       </c>
       <c r="AJ17" s="13">
-        <f>AI17+AJ16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AJ16),0)</f>
         <v/>
       </c>
       <c r="AK17" s="13">
-        <f>AJ17+AK16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AK16),0)</f>
         <v/>
       </c>
       <c r="AL17" s="13">
-        <f>AK17+AL16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AL16),0)</f>
         <v/>
       </c>
       <c r="AM17" s="13">
-        <f>AL17+AM16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AM16),0)</f>
         <v/>
       </c>
       <c r="AN17" s="13">
-        <f>AM17+AN16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AN16),0)</f>
         <v/>
       </c>
       <c r="AO17" s="13">
-        <f>AN17+AO16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AO16),0)</f>
         <v/>
       </c>
       <c r="AP17" s="13">
-        <f>AO17+AP16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AP16),0)</f>
         <v/>
       </c>
       <c r="AQ17" s="13">
-        <f>AP17+AQ16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AQ16),0)</f>
         <v/>
       </c>
       <c r="AR17" s="13">
-        <f>AQ17+AR16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AR16),0)</f>
         <v/>
       </c>
       <c r="AS17" s="13">
-        <f>AR17+AS16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AS16),0)</f>
         <v/>
       </c>
       <c r="AT17" s="13">
-        <f>AS17+AT16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AT16),0)</f>
         <v/>
       </c>
       <c r="AU17" s="13">
-        <f>AT17+AU16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AU16),0)</f>
         <v/>
       </c>
       <c r="AV17" s="13">
-        <f>AU17+AV16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AV16),0)</f>
         <v/>
       </c>
       <c r="AW17" s="13">
-        <f>AV17+AW16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AW16),0)</f>
         <v/>
       </c>
       <c r="AX17" s="13">
-        <f>AW17+AX16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AX16),0)</f>
         <v/>
       </c>
       <c r="AY17" s="13">
-        <f>AX17+AY16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AY16),0)</f>
         <v/>
       </c>
       <c r="AZ17" s="13">
-        <f>AY17+AZ16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:AZ16),0)</f>
         <v/>
       </c>
       <c r="BA17" s="13">
-        <f>AZ17+BA16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:BA16),0)</f>
         <v/>
       </c>
       <c r="BB17" s="13">
-        <f>BA17+BB16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:BB16),0)</f>
         <v/>
       </c>
       <c r="BC17" s="13">
-        <f>BB17+BC16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:BC16),0)</f>
         <v/>
       </c>
       <c r="BD17" s="13">
-        <f>BC17+BD16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:BD16),0)</f>
         <v/>
       </c>
       <c r="BE17" s="13">
-        <f>BD17+BE16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:BE16),0)</f>
         <v/>
       </c>
       <c r="BF17" s="13">
-        <f>BE17+BF16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:BF16),0)</f>
         <v/>
       </c>
       <c r="BG17" s="13">
-        <f>BF17+BG16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:BG16),0)</f>
         <v/>
       </c>
       <c r="BH17" s="13">
-        <f>BG17+BH16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:BH16),0)</f>
         <v/>
       </c>
       <c r="BI17" s="13">
-        <f>BH17+BI16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:BI16),0)</f>
         <v/>
       </c>
       <c r="BJ17" s="13">
-        <f>BI17+BJ16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:BJ16),0)</f>
         <v/>
       </c>
       <c r="BK17" s="13">
-        <f>BJ17+BK16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:BK16),0)</f>
         <v/>
       </c>
       <c r="BL17" s="13">
-        <f>BK17+BL16</f>
+        <f>ROUNDDOWN(Assumptions!$D$60+SUM($E16:BL16),0)</f>
         <v/>
       </c>
       <c r="BN17" s="66">
@@ -23275,6 +23275,11 @@
         <f>BL17</f>
         <v/>
       </c>
+      <c r="BT17" s="32" t="inlineStr">
+        <is>
+          <t>whole people only, so half a rep a month means one every second month</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
@@ -23556,277 +23561,277 @@
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Installer partners signed</t>
+          <t>Partner signing rate</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>partners</t>
-        </is>
-      </c>
-      <c r="E19" s="13">
+          <t>partners/month</t>
+        </is>
+      </c>
+      <c r="E19" s="64">
         <f>IF(E$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(E$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="64">
         <f>IF(F$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(F$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="64">
         <f>IF(G$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(G$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="H19" s="13">
+      <c r="H19" s="64">
         <f>IF(H$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(H$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="64">
         <f>IF(I$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(I$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="J19" s="13">
+      <c r="J19" s="64">
         <f>IF(J$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(J$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="K19" s="13">
+      <c r="K19" s="64">
         <f>IF(K$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(K$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="L19" s="13">
+      <c r="L19" s="64">
         <f>IF(L$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(L$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="M19" s="13">
+      <c r="M19" s="64">
         <f>IF(M$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(M$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="N19" s="13">
+      <c r="N19" s="64">
         <f>IF(N$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(N$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="O19" s="13">
+      <c r="O19" s="64">
         <f>IF(O$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(O$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="P19" s="13">
+      <c r="P19" s="64">
         <f>IF(P$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(P$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="Q19" s="13">
+      <c r="Q19" s="64">
         <f>IF(Q$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(Q$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="R19" s="13">
+      <c r="R19" s="64">
         <f>IF(R$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(R$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="S19" s="13">
+      <c r="S19" s="64">
         <f>IF(S$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(S$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="T19" s="13">
+      <c r="T19" s="64">
         <f>IF(T$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(T$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="U19" s="13">
+      <c r="U19" s="64">
         <f>IF(U$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(U$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="V19" s="13">
+      <c r="V19" s="64">
         <f>IF(V$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(V$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="W19" s="13">
+      <c r="W19" s="64">
         <f>IF(W$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(W$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="X19" s="13">
+      <c r="X19" s="64">
         <f>IF(X$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(X$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="Y19" s="13">
+      <c r="Y19" s="64">
         <f>IF(Y$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(Y$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="Z19" s="13">
+      <c r="Z19" s="64">
         <f>IF(Z$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(Z$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AA19" s="13">
+      <c r="AA19" s="64">
         <f>IF(AA$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AA$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AB19" s="13">
+      <c r="AB19" s="64">
         <f>IF(AB$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AB$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AC19" s="13">
+      <c r="AC19" s="64">
         <f>IF(AC$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AC$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AD19" s="13">
+      <c r="AD19" s="64">
         <f>IF(AD$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AD$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AE19" s="13">
+      <c r="AE19" s="64">
         <f>IF(AE$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AE$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AF19" s="13">
+      <c r="AF19" s="64">
         <f>IF(AF$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AF$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AG19" s="13">
+      <c r="AG19" s="64">
         <f>IF(AG$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AG$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AH19" s="13">
+      <c r="AH19" s="64">
         <f>IF(AH$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AH$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AI19" s="13">
+      <c r="AI19" s="64">
         <f>IF(AI$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AI$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AJ19" s="13">
+      <c r="AJ19" s="64">
         <f>IF(AJ$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AJ$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AK19" s="13">
+      <c r="AK19" s="64">
         <f>IF(AK$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AK$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AL19" s="13">
+      <c r="AL19" s="64">
         <f>IF(AL$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AL$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AM19" s="13">
+      <c r="AM19" s="64">
         <f>IF(AM$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AM$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AN19" s="13">
+      <c r="AN19" s="64">
         <f>IF(AN$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AN$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AO19" s="13">
+      <c r="AO19" s="64">
         <f>IF(AO$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AO$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AP19" s="13">
+      <c r="AP19" s="64">
         <f>IF(AP$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AP$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AQ19" s="13">
+      <c r="AQ19" s="64">
         <f>IF(AQ$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AQ$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AR19" s="13">
+      <c r="AR19" s="64">
         <f>IF(AR$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AR$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AS19" s="13">
+      <c r="AS19" s="64">
         <f>IF(AS$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AS$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AT19" s="13">
+      <c r="AT19" s="64">
         <f>IF(AT$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AT$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AU19" s="13">
+      <c r="AU19" s="64">
         <f>IF(AU$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AU$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AV19" s="13">
+      <c r="AV19" s="64">
         <f>IF(AV$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AV$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AW19" s="13">
+      <c r="AW19" s="64">
         <f>IF(AW$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AW$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AX19" s="13">
+      <c r="AX19" s="64">
         <f>IF(AX$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AX$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AY19" s="13">
+      <c r="AY19" s="64">
         <f>IF(AY$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AY$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="AZ19" s="13">
+      <c r="AZ19" s="64">
         <f>IF(AZ$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(AZ$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BA19" s="13">
+      <c r="BA19" s="64">
         <f>IF(BA$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(BA$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BB19" s="13">
+      <c r="BB19" s="64">
         <f>IF(BB$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(BB$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BC19" s="13">
+      <c r="BC19" s="64">
         <f>IF(BC$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(BC$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BD19" s="13">
+      <c r="BD19" s="64">
         <f>IF(BD$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(BD$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BE19" s="13">
+      <c r="BE19" s="64">
         <f>IF(BE$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(BE$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BF19" s="13">
+      <c r="BF19" s="64">
         <f>IF(BF$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(BF$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BG19" s="13">
+      <c r="BG19" s="64">
         <f>IF(BG$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(BG$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BH19" s="13">
+      <c r="BH19" s="64">
         <f>IF(BH$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(BH$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BI19" s="13">
+      <c r="BI19" s="64">
         <f>IF(BI$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(BI$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BJ19" s="13">
+      <c r="BJ19" s="64">
         <f>IF(BJ$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(BJ$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BK19" s="13">
+      <c r="BK19" s="64">
         <f>IF(BK$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(BK$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BL19" s="13">
+      <c r="BL19" s="64">
         <f>IF(BL$3&lt;Assumptions!$D$11,0,HLOOKUP(YEAR(BL$3),Assumptions!$D$55:$H$56,2,FALSE))</f>
         <v/>
       </c>
-      <c r="BN19" s="66">
+      <c r="BN19" s="65">
         <f>SUM(E19:P19)</f>
         <v/>
       </c>
-      <c r="BO19" s="66">
+      <c r="BO19" s="65">
         <f>SUM(Q19:AB19)</f>
         <v/>
       </c>
-      <c r="BP19" s="66">
+      <c r="BP19" s="65">
         <f>SUM(AC19:AN19)</f>
         <v/>
       </c>
-      <c r="BQ19" s="66">
+      <c r="BQ19" s="65">
         <f>SUM(AO19:AZ19)</f>
         <v/>
       </c>
-      <c r="BR19" s="66">
+      <c r="BR19" s="65">
         <f>SUM(BA19:BL19)</f>
         <v/>
       </c>
       <c r="BT19" s="32" t="inlineStr">
         <is>
-          <t>no partner intros before the first month we can sell</t>
+          <t>the planned rate, which can be less than one a month</t>
         </is>
       </c>
     </row>
@@ -23842,243 +23847,243 @@
         </is>
       </c>
       <c r="E20" s="13">
-        <f>Assumptions!$D$62+E19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:E19),0)</f>
         <v/>
       </c>
       <c r="F20" s="13">
-        <f>E20+F19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:F19),0)</f>
         <v/>
       </c>
       <c r="G20" s="13">
-        <f>F20+G19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:G19),0)</f>
         <v/>
       </c>
       <c r="H20" s="13">
-        <f>G20+H19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:H19),0)</f>
         <v/>
       </c>
       <c r="I20" s="13">
-        <f>H20+I19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:I19),0)</f>
         <v/>
       </c>
       <c r="J20" s="13">
-        <f>I20+J19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:J19),0)</f>
         <v/>
       </c>
       <c r="K20" s="13">
-        <f>J20+K19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:K19),0)</f>
         <v/>
       </c>
       <c r="L20" s="13">
-        <f>K20+L19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:L19),0)</f>
         <v/>
       </c>
       <c r="M20" s="13">
-        <f>L20+M19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:M19),0)</f>
         <v/>
       </c>
       <c r="N20" s="13">
-        <f>M20+N19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:N19),0)</f>
         <v/>
       </c>
       <c r="O20" s="13">
-        <f>N20+O19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:O19),0)</f>
         <v/>
       </c>
       <c r="P20" s="13">
-        <f>O20+P19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:P19),0)</f>
         <v/>
       </c>
       <c r="Q20" s="13">
-        <f>P20+Q19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:Q19),0)</f>
         <v/>
       </c>
       <c r="R20" s="13">
-        <f>Q20+R19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:R19),0)</f>
         <v/>
       </c>
       <c r="S20" s="13">
-        <f>R20+S19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:S19),0)</f>
         <v/>
       </c>
       <c r="T20" s="13">
-        <f>S20+T19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:T19),0)</f>
         <v/>
       </c>
       <c r="U20" s="13">
-        <f>T20+U19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:U19),0)</f>
         <v/>
       </c>
       <c r="V20" s="13">
-        <f>U20+V19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:V19),0)</f>
         <v/>
       </c>
       <c r="W20" s="13">
-        <f>V20+W19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:W19),0)</f>
         <v/>
       </c>
       <c r="X20" s="13">
-        <f>W20+X19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:X19),0)</f>
         <v/>
       </c>
       <c r="Y20" s="13">
-        <f>X20+Y19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:Y19),0)</f>
         <v/>
       </c>
       <c r="Z20" s="13">
-        <f>Y20+Z19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:Z19),0)</f>
         <v/>
       </c>
       <c r="AA20" s="13">
-        <f>Z20+AA19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AA19),0)</f>
         <v/>
       </c>
       <c r="AB20" s="13">
-        <f>AA20+AB19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AB19),0)</f>
         <v/>
       </c>
       <c r="AC20" s="13">
-        <f>AB20+AC19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AC19),0)</f>
         <v/>
       </c>
       <c r="AD20" s="13">
-        <f>AC20+AD19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AD19),0)</f>
         <v/>
       </c>
       <c r="AE20" s="13">
-        <f>AD20+AE19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AE19),0)</f>
         <v/>
       </c>
       <c r="AF20" s="13">
-        <f>AE20+AF19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AF19),0)</f>
         <v/>
       </c>
       <c r="AG20" s="13">
-        <f>AF20+AG19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AG19),0)</f>
         <v/>
       </c>
       <c r="AH20" s="13">
-        <f>AG20+AH19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AH19),0)</f>
         <v/>
       </c>
       <c r="AI20" s="13">
-        <f>AH20+AI19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AI19),0)</f>
         <v/>
       </c>
       <c r="AJ20" s="13">
-        <f>AI20+AJ19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AJ19),0)</f>
         <v/>
       </c>
       <c r="AK20" s="13">
-        <f>AJ20+AK19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AK19),0)</f>
         <v/>
       </c>
       <c r="AL20" s="13">
-        <f>AK20+AL19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AL19),0)</f>
         <v/>
       </c>
       <c r="AM20" s="13">
-        <f>AL20+AM19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AM19),0)</f>
         <v/>
       </c>
       <c r="AN20" s="13">
-        <f>AM20+AN19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AN19),0)</f>
         <v/>
       </c>
       <c r="AO20" s="13">
-        <f>AN20+AO19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AO19),0)</f>
         <v/>
       </c>
       <c r="AP20" s="13">
-        <f>AO20+AP19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AP19),0)</f>
         <v/>
       </c>
       <c r="AQ20" s="13">
-        <f>AP20+AQ19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AQ19),0)</f>
         <v/>
       </c>
       <c r="AR20" s="13">
-        <f>AQ20+AR19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AR19),0)</f>
         <v/>
       </c>
       <c r="AS20" s="13">
-        <f>AR20+AS19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AS19),0)</f>
         <v/>
       </c>
       <c r="AT20" s="13">
-        <f>AS20+AT19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AT19),0)</f>
         <v/>
       </c>
       <c r="AU20" s="13">
-        <f>AT20+AU19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AU19),0)</f>
         <v/>
       </c>
       <c r="AV20" s="13">
-        <f>AU20+AV19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AV19),0)</f>
         <v/>
       </c>
       <c r="AW20" s="13">
-        <f>AV20+AW19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AW19),0)</f>
         <v/>
       </c>
       <c r="AX20" s="13">
-        <f>AW20+AX19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AX19),0)</f>
         <v/>
       </c>
       <c r="AY20" s="13">
-        <f>AX20+AY19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AY19),0)</f>
         <v/>
       </c>
       <c r="AZ20" s="13">
-        <f>AY20+AZ19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:AZ19),0)</f>
         <v/>
       </c>
       <c r="BA20" s="13">
-        <f>AZ20+BA19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:BA19),0)</f>
         <v/>
       </c>
       <c r="BB20" s="13">
-        <f>BA20+BB19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:BB19),0)</f>
         <v/>
       </c>
       <c r="BC20" s="13">
-        <f>BB20+BC19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:BC19),0)</f>
         <v/>
       </c>
       <c r="BD20" s="13">
-        <f>BC20+BD19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:BD19),0)</f>
         <v/>
       </c>
       <c r="BE20" s="13">
-        <f>BD20+BE19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:BE19),0)</f>
         <v/>
       </c>
       <c r="BF20" s="13">
-        <f>BE20+BF19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:BF19),0)</f>
         <v/>
       </c>
       <c r="BG20" s="13">
-        <f>BF20+BG19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:BG19),0)</f>
         <v/>
       </c>
       <c r="BH20" s="13">
-        <f>BG20+BH19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:BH19),0)</f>
         <v/>
       </c>
       <c r="BI20" s="13">
-        <f>BH20+BI19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:BI19),0)</f>
         <v/>
       </c>
       <c r="BJ20" s="13">
-        <f>BI20+BJ19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:BJ19),0)</f>
         <v/>
       </c>
       <c r="BK20" s="13">
-        <f>BJ20+BK19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:BK19),0)</f>
         <v/>
       </c>
       <c r="BL20" s="13">
-        <f>BK20+BL19</f>
+        <f>ROUNDDOWN(Assumptions!$D$62+SUM($E19:BL19),0)</f>
         <v/>
       </c>
       <c r="BN20" s="66">
@@ -24100,6 +24105,11 @@
       <c r="BR20" s="66">
         <f>BL20</f>
         <v/>
+      </c>
+      <c r="BT20" s="32" t="inlineStr">
+        <is>
+          <t>whole partners only, signed as the running total passes each whole number</t>
+        </is>
       </c>
     </row>
     <row r="21">

--- a/models/Tarnoc_v2_aggressive_2026-09-07.xlsx
+++ b/models/Tarnoc_v2_aggressive_2026-09-07.xlsx
@@ -27095,243 +27095,243 @@
         </is>
       </c>
       <c r="E39" s="9">
-        <f>E34*Assumptions!$D$25</f>
+        <f>ROUND(E34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="F39" s="9">
-        <f>F34*Assumptions!$D$25</f>
+        <f>ROUND(F34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="G39" s="9">
-        <f>G34*Assumptions!$D$25</f>
+        <f>ROUND(G34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="H39" s="9">
-        <f>H34*Assumptions!$D$25</f>
+        <f>ROUND(H34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="I39" s="9">
-        <f>I34*Assumptions!$D$25</f>
+        <f>ROUND(I34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="J39" s="9">
-        <f>J34*Assumptions!$D$25</f>
+        <f>ROUND(J34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="K39" s="9">
-        <f>K34*Assumptions!$D$25</f>
+        <f>ROUND(K34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="L39" s="9">
-        <f>L34*Assumptions!$D$25</f>
+        <f>ROUND(L34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="M39" s="9">
-        <f>M34*Assumptions!$D$25</f>
+        <f>ROUND(M34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="N39" s="9">
-        <f>N34*Assumptions!$D$25</f>
+        <f>ROUND(N34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="O39" s="9">
-        <f>O34*Assumptions!$D$25</f>
+        <f>ROUND(O34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="P39" s="9">
-        <f>P34*Assumptions!$D$25</f>
+        <f>ROUND(P34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="Q39" s="9">
-        <f>Q34*Assumptions!$D$25</f>
+        <f>ROUND(Q34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="R39" s="9">
-        <f>R34*Assumptions!$D$25</f>
+        <f>ROUND(R34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="S39" s="9">
-        <f>S34*Assumptions!$D$25</f>
+        <f>ROUND(S34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="T39" s="9">
-        <f>T34*Assumptions!$D$25</f>
+        <f>ROUND(T34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="U39" s="9">
-        <f>U34*Assumptions!$D$25</f>
+        <f>ROUND(U34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="V39" s="9">
-        <f>V34*Assumptions!$D$25</f>
+        <f>ROUND(V34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="W39" s="9">
-        <f>W34*Assumptions!$D$25</f>
+        <f>ROUND(W34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="X39" s="9">
-        <f>X34*Assumptions!$D$25</f>
+        <f>ROUND(X34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="Y39" s="9">
-        <f>Y34*Assumptions!$D$25</f>
+        <f>ROUND(Y34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="Z39" s="9">
-        <f>Z34*Assumptions!$D$25</f>
+        <f>ROUND(Z34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AA39" s="9">
-        <f>AA34*Assumptions!$D$25</f>
+        <f>ROUND(AA34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AB39" s="9">
-        <f>AB34*Assumptions!$D$25</f>
+        <f>ROUND(AB34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AC39" s="9">
-        <f>AC34*Assumptions!$D$25</f>
+        <f>ROUND(AC34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AD39" s="9">
-        <f>AD34*Assumptions!$D$25</f>
+        <f>ROUND(AD34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AE39" s="9">
-        <f>AE34*Assumptions!$D$25</f>
+        <f>ROUND(AE34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AF39" s="9">
-        <f>AF34*Assumptions!$D$25</f>
+        <f>ROUND(AF34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AG39" s="9">
-        <f>AG34*Assumptions!$D$25</f>
+        <f>ROUND(AG34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AH39" s="9">
-        <f>AH34*Assumptions!$D$25</f>
+        <f>ROUND(AH34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AI39" s="9">
-        <f>AI34*Assumptions!$D$25</f>
+        <f>ROUND(AI34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AJ39" s="9">
-        <f>AJ34*Assumptions!$D$25</f>
+        <f>ROUND(AJ34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AK39" s="9">
-        <f>AK34*Assumptions!$D$25</f>
+        <f>ROUND(AK34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AL39" s="9">
-        <f>AL34*Assumptions!$D$25</f>
+        <f>ROUND(AL34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AM39" s="9">
-        <f>AM34*Assumptions!$D$25</f>
+        <f>ROUND(AM34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AN39" s="9">
-        <f>AN34*Assumptions!$D$25</f>
+        <f>ROUND(AN34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AO39" s="9">
-        <f>AO34*Assumptions!$D$25</f>
+        <f>ROUND(AO34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AP39" s="9">
-        <f>AP34*Assumptions!$D$25</f>
+        <f>ROUND(AP34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AQ39" s="9">
-        <f>AQ34*Assumptions!$D$25</f>
+        <f>ROUND(AQ34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AR39" s="9">
-        <f>AR34*Assumptions!$D$25</f>
+        <f>ROUND(AR34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AS39" s="9">
-        <f>AS34*Assumptions!$D$25</f>
+        <f>ROUND(AS34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AT39" s="9">
-        <f>AT34*Assumptions!$D$25</f>
+        <f>ROUND(AT34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AU39" s="9">
-        <f>AU34*Assumptions!$D$25</f>
+        <f>ROUND(AU34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AV39" s="9">
-        <f>AV34*Assumptions!$D$25</f>
+        <f>ROUND(AV34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AW39" s="9">
-        <f>AW34*Assumptions!$D$25</f>
+        <f>ROUND(AW34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AX39" s="9">
-        <f>AX34*Assumptions!$D$25</f>
+        <f>ROUND(AX34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AY39" s="9">
-        <f>AY34*Assumptions!$D$25</f>
+        <f>ROUND(AY34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="AZ39" s="9">
-        <f>AZ34*Assumptions!$D$25</f>
+        <f>ROUND(AZ34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BA39" s="9">
-        <f>BA34*Assumptions!$D$25</f>
+        <f>ROUND(BA34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BB39" s="9">
-        <f>BB34*Assumptions!$D$25</f>
+        <f>ROUND(BB34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BC39" s="9">
-        <f>BC34*Assumptions!$D$25</f>
+        <f>ROUND(BC34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BD39" s="9">
-        <f>BD34*Assumptions!$D$25</f>
+        <f>ROUND(BD34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BE39" s="9">
-        <f>BE34*Assumptions!$D$25</f>
+        <f>ROUND(BE34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BF39" s="9">
-        <f>BF34*Assumptions!$D$25</f>
+        <f>ROUND(BF34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BG39" s="9">
-        <f>BG34*Assumptions!$D$25</f>
+        <f>ROUND(BG34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BH39" s="9">
-        <f>BH34*Assumptions!$D$25</f>
+        <f>ROUND(BH34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BI39" s="9">
-        <f>BI34*Assumptions!$D$25</f>
+        <f>ROUND(BI34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BJ39" s="9">
-        <f>BJ34*Assumptions!$D$25</f>
+        <f>ROUND(BJ34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BK39" s="9">
-        <f>BK34*Assumptions!$D$25</f>
+        <f>ROUND(BK34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BL39" s="9">
-        <f>BL34*Assumptions!$D$25</f>
+        <f>ROUND(BL34*Assumptions!$D$25,0)</f>
         <v/>
       </c>
       <c r="BN39" s="60">
@@ -27354,6 +27354,11 @@
         <f>SUM(BA39:BL39)</f>
         <v/>
       </c>
+      <c r="BT39" s="32" t="inlineStr">
+        <is>
+          <t>whole units, and the Combi+ row takes the remainder so the two add to units sold</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="B40" s="6" t="inlineStr">
@@ -27367,243 +27372,243 @@
         </is>
       </c>
       <c r="E40" s="9">
-        <f>E34*Assumptions!$D$26</f>
+        <f>E34-E39</f>
         <v/>
       </c>
       <c r="F40" s="9">
-        <f>F34*Assumptions!$D$26</f>
+        <f>F34-F39</f>
         <v/>
       </c>
       <c r="G40" s="9">
-        <f>G34*Assumptions!$D$26</f>
+        <f>G34-G39</f>
         <v/>
       </c>
       <c r="H40" s="9">
-        <f>H34*Assumptions!$D$26</f>
+        <f>H34-H39</f>
         <v/>
       </c>
       <c r="I40" s="9">
-        <f>I34*Assumptions!$D$26</f>
+        <f>I34-I39</f>
         <v/>
       </c>
       <c r="J40" s="9">
-        <f>J34*Assumptions!$D$26</f>
+        <f>J34-J39</f>
         <v/>
       </c>
       <c r="K40" s="9">
-        <f>K34*Assumptions!$D$26</f>
+        <f>K34-K39</f>
         <v/>
       </c>
       <c r="L40" s="9">
-        <f>L34*Assumptions!$D$26</f>
+        <f>L34-L39</f>
         <v/>
       </c>
       <c r="M40" s="9">
-        <f>M34*Assumptions!$D$26</f>
+        <f>M34-M39</f>
         <v/>
       </c>
       <c r="N40" s="9">
-        <f>N34*Assumptions!$D$26</f>
+        <f>N34-N39</f>
         <v/>
       </c>
       <c r="O40" s="9">
-        <f>O34*Assumptions!$D$26</f>
+        <f>O34-O39</f>
         <v/>
       </c>
       <c r="P40" s="9">
-        <f>P34*Assumptions!$D$26</f>
+        <f>P34-P39</f>
         <v/>
       </c>
       <c r="Q40" s="9">
-        <f>Q34*Assumptions!$D$26</f>
+        <f>Q34-Q39</f>
         <v/>
       </c>
       <c r="R40" s="9">
-        <f>R34*Assumptions!$D$26</f>
+        <f>R34-R39</f>
         <v/>
       </c>
       <c r="S40" s="9">
-        <f>S34*Assumptions!$D$26</f>
+        <f>S34-S39</f>
         <v/>
       </c>
       <c r="T40" s="9">
-        <f>T34*Assumptions!$D$26</f>
+        <f>T34-T39</f>
         <v/>
       </c>
       <c r="U40" s="9">
-        <f>U34*Assumptions!$D$26</f>
+        <f>U34-U39</f>
         <v/>
       </c>
       <c r="V40" s="9">
-        <f>V34*Assumptions!$D$26</f>
+        <f>V34-V39</f>
         <v/>
       </c>
       <c r="W40" s="9">
-        <f>W34*Assumptions!$D$26</f>
+        <f>W34-W39</f>
         <v/>
       </c>
       <c r="X40" s="9">
-        <f>X34*Assumptions!$D$26</f>
+        <f>X34-X39</f>
         <v/>
       </c>
       <c r="Y40" s="9">
-        <f>Y34*Assumptions!$D$26</f>
+        <f>Y34-Y39</f>
         <v/>
       </c>
       <c r="Z40" s="9">
-        <f>Z34*Assumptions!$D$26</f>
+        <f>Z34-Z39</f>
         <v/>
       </c>
       <c r="AA40" s="9">
-        <f>AA34*Assumptions!$D$26</f>
+        <f>AA34-AA39</f>
         <v/>
       </c>
       <c r="AB40" s="9">
-        <f>AB34*Assumptions!$D$26</f>
+        <f>AB34-AB39</f>
         <v/>
       </c>
       <c r="AC40" s="9">
-        <f>AC34*Assumptions!$D$26</f>
+        <f>AC34-AC39</f>
         <v/>
       </c>
       <c r="AD40" s="9">
-        <f>AD34*Assumptions!$D$26</f>
+        <f>AD34-AD39</f>
         <v/>
       </c>
       <c r="AE40" s="9">
-        <f>AE34*Assumptions!$D$26</f>
+        <f>AE34-AE39</f>
         <v/>
       </c>
       <c r="AF40" s="9">
-        <f>AF34*Assumptions!$D$26</f>
+        <f>AF34-AF39</f>
         <v/>
       </c>
       <c r="AG40" s="9">
-        <f>AG34*Assumptions!$D$26</f>
+        <f>AG34-AG39</f>
         <v/>
       </c>
       <c r="AH40" s="9">
-        <f>AH34*Assumptions!$D$26</f>
+        <f>AH34-AH39</f>
         <v/>
       </c>
       <c r="AI40" s="9">
-        <f>AI34*Assumptions!$D$26</f>
+        <f>AI34-AI39</f>
         <v/>
       </c>
       <c r="AJ40" s="9">
-        <f>AJ34*Assumptions!$D$26</f>
+        <f>AJ34-AJ39</f>
         <v/>
       </c>
       <c r="AK40" s="9">
-        <f>AK34*Assumptions!$D$26</f>
+        <f>AK34-AK39</f>
         <v/>
       </c>
       <c r="AL40" s="9">
-        <f>AL34*Assumptions!$D$26</f>
+        <f>AL34-AL39</f>
         <v/>
       </c>
       <c r="AM40" s="9">
-        <f>AM34*Assumptions!$D$26</f>
+        <f>AM34-AM39</f>
         <v/>
       </c>
       <c r="AN40" s="9">
-        <f>AN34*Assumptions!$D$26</f>
+        <f>AN34-AN39</f>
         <v/>
       </c>
       <c r="AO40" s="9">
-        <f>AO34*Assumptions!$D$26</f>
+        <f>AO34-AO39</f>
         <v/>
       </c>
       <c r="AP40" s="9">
-        <f>AP34*Assumptions!$D$26</f>
+        <f>AP34-AP39</f>
         <v/>
       </c>
       <c r="AQ40" s="9">
-        <f>AQ34*Assumptions!$D$26</f>
+        <f>AQ34-AQ39</f>
         <v/>
       </c>
       <c r="AR40" s="9">
-        <f>AR34*Assumptions!$D$26</f>
+        <f>AR34-AR39</f>
         <v/>
       </c>
       <c r="AS40" s="9">
-        <f>AS34*Assumptions!$D$26</f>
+        <f>AS34-AS39</f>
         <v/>
       </c>
       <c r="AT40" s="9">
-        <f>AT34*Assumptions!$D$26</f>
+        <f>AT34-AT39</f>
         <v/>
       </c>
       <c r="AU40" s="9">
-        <f>AU34*Assumptions!$D$26</f>
+        <f>AU34-AU39</f>
         <v/>
       </c>
       <c r="AV40" s="9">
-        <f>AV34*Assumptions!$D$26</f>
+        <f>AV34-AV39</f>
         <v/>
       </c>
       <c r="AW40" s="9">
-        <f>AW34*Assumptions!$D$26</f>
+        <f>AW34-AW39</f>
         <v/>
       </c>
       <c r="AX40" s="9">
-        <f>AX34*Assumptions!$D$26</f>
+        <f>AX34-AX39</f>
         <v/>
       </c>
       <c r="AY40" s="9">
-        <f>AY34*Assumptions!$D$26</f>
+        <f>AY34-AY39</f>
         <v/>
       </c>
       <c r="AZ40" s="9">
-        <f>AZ34*Assumptions!$D$26</f>
+        <f>AZ34-AZ39</f>
         <v/>
       </c>
       <c r="BA40" s="9">
-        <f>BA34*Assumptions!$D$26</f>
+        <f>BA34-BA39</f>
         <v/>
       </c>
       <c r="BB40" s="9">
-        <f>BB34*Assumptions!$D$26</f>
+        <f>BB34-BB39</f>
         <v/>
       </c>
       <c r="BC40" s="9">
-        <f>BC34*Assumptions!$D$26</f>
+        <f>BC34-BC39</f>
         <v/>
       </c>
       <c r="BD40" s="9">
-        <f>BD34*Assumptions!$D$26</f>
+        <f>BD34-BD39</f>
         <v/>
       </c>
       <c r="BE40" s="9">
-        <f>BE34*Assumptions!$D$26</f>
+        <f>BE34-BE39</f>
         <v/>
       </c>
       <c r="BF40" s="9">
-        <f>BF34*Assumptions!$D$26</f>
+        <f>BF34-BF39</f>
         <v/>
       </c>
       <c r="BG40" s="9">
-        <f>BG34*Assumptions!$D$26</f>
+        <f>BG34-BG39</f>
         <v/>
       </c>
       <c r="BH40" s="9">
-        <f>BH34*Assumptions!$D$26</f>
+        <f>BH34-BH39</f>
         <v/>
       </c>
       <c r="BI40" s="9">
-        <f>BI34*Assumptions!$D$26</f>
+        <f>BI34-BI39</f>
         <v/>
       </c>
       <c r="BJ40" s="9">
-        <f>BJ34*Assumptions!$D$26</f>
+        <f>BJ34-BJ39</f>
         <v/>
       </c>
       <c r="BK40" s="9">
-        <f>BK34*Assumptions!$D$26</f>
+        <f>BK34-BK39</f>
         <v/>
       </c>
       <c r="BL40" s="9">
-        <f>BL34*Assumptions!$D$26</f>
+        <f>BL34-BL39</f>
         <v/>
       </c>
       <c r="BN40" s="60">
